--- a/FORMATO DE COMPARATIVA.xlsx
+++ b/FORMATO DE COMPARATIVA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\MACHOTES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\ComprasUUC\Ejemplo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4682BFC5-8950-4E1A-B2AE-684730EC869B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EB000A-9BA4-4FA3-9480-80FEB73C7FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">UNAUNCUARTO!$B$12:$H$78</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">UNAUNCUARTO!$A$1:$X$92</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">UNAUNCUARTO!$A$1:$AA$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>OBRA:</t>
   </si>
@@ -143,6 +143,18 @@
   </si>
   <si>
     <t>Proveedor 2</t>
+  </si>
+  <si>
+    <t>Elige un proveedor</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P3</t>
   </si>
 </sst>
 </file>
@@ -422,7 +434,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,8 +495,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="62">
+  <borders count="70">
     <border>
       <left/>
       <right/>
@@ -1307,12 +1325,92 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1675,37 +1773,28 @@
     <xf numFmtId="2" fontId="16" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="33" fillId="8" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="33" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1729,6 +1818,12 @@
     <xf numFmtId="0" fontId="33" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="33" fillId="8" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="33" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1741,12 +1836,49 @@
     <xf numFmtId="0" fontId="33" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="3" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2042,10 +2174,10 @@
     <col min="5" max="5" width="18.42578125" customWidth="1"/>
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
-    <col min="8" max="9" width="21.42578125" style="21" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="21.42578125" style="21" customWidth="1"/>
     <col min="10" max="11" width="21.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" customWidth="1"/>
     <col min="14" max="14" width="19.85546875" customWidth="1"/>
     <col min="15" max="15" width="33.85546875" customWidth="1"/>
     <col min="16" max="16" width="18.42578125" customWidth="1"/>
@@ -2054,7 +2186,7 @@
     <col min="19" max="20" width="18.42578125" customWidth="1"/>
     <col min="21" max="21" width="45" customWidth="1"/>
     <col min="22" max="23" width="18.42578125" customWidth="1"/>
-    <col min="24" max="24" width="1.85546875" customWidth="1"/>
+    <col min="24" max="24" width="11.28515625" customWidth="1"/>
     <col min="25" max="25" width="11.42578125" customWidth="1"/>
     <col min="26" max="39" width="8.85546875" customWidth="1"/>
   </cols>
@@ -2102,33 +2234,33 @@
     </row>
     <row r="3" spans="1:39" s="11" customFormat="1" ht="31.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
-      <c r="B3" s="139" t="s">
+      <c r="B3" s="142" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139"/>
-      <c r="N3" s="139"/>
-      <c r="O3" s="139"/>
-      <c r="P3" s="139"/>
-      <c r="Q3" s="139"/>
-      <c r="R3" s="139"/>
-      <c r="S3" s="139"/>
-      <c r="T3" s="139"/>
-      <c r="U3" s="139"/>
-      <c r="V3" s="139"/>
-      <c r="W3" s="139"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
+      <c r="C3" s="142"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="142"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="142"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="142"/>
+      <c r="J3" s="142"/>
+      <c r="K3" s="142"/>
+      <c r="L3" s="142"/>
+      <c r="M3" s="142"/>
+      <c r="N3" s="142"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
+      <c r="S3" s="142"/>
+      <c r="T3" s="142"/>
+      <c r="U3" s="142"/>
+      <c r="V3" s="142"/>
+      <c r="W3" s="142"/>
+      <c r="X3" s="142"/>
+      <c r="Y3" s="142"/>
+      <c r="Z3" s="142"/>
       <c r="AA3" s="10"/>
       <c r="AB3" s="10"/>
       <c r="AC3" s="10"/>
@@ -2495,63 +2627,65 @@
     </row>
     <row r="12" spans="1:39" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="140" t="s">
+      <c r="B12" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="142" t="s">
+      <c r="C12" s="145" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="142" t="s">
+      <c r="D12" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="142" t="s">
+      <c r="E12" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="142" t="s">
+      <c r="F12" s="145" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="144" t="s">
+      <c r="G12" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="130">
-        <v>-5.0000000000000001E-4</v>
-      </c>
-      <c r="I12" s="130" t="s">
+      <c r="H12" s="149">
+        <v>0.05</v>
+      </c>
+      <c r="I12" s="149" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="144" t="s">
+      <c r="J12" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="144" t="s">
+      <c r="K12" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="L12" s="148" t="s">
+      <c r="L12" s="153" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="128" t="s">
+      <c r="M12" s="155" t="s">
         <v>13</v>
       </c>
-      <c r="N12" s="146" t="s">
+      <c r="N12" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="O12" s="132" t="s">
+      <c r="O12" s="157" t="s">
         <v>31</v>
       </c>
-      <c r="P12" s="133"/>
-      <c r="Q12" s="134"/>
-      <c r="R12" s="135" t="s">
+      <c r="P12" s="138"/>
+      <c r="Q12" s="158"/>
+      <c r="R12" s="159" t="s">
         <v>33</v>
       </c>
-      <c r="S12" s="136"/>
-      <c r="T12" s="137"/>
-      <c r="U12" s="133" t="s">
+      <c r="S12" s="160"/>
+      <c r="T12" s="161"/>
+      <c r="U12" s="138" t="s">
         <v>32</v>
       </c>
-      <c r="V12" s="133"/>
-      <c r="W12" s="138"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-      <c r="Z12" s="1"/>
+      <c r="V12" s="138"/>
+      <c r="W12" s="139"/>
+      <c r="X12" s="140" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y12" s="140"/>
+      <c r="Z12" s="141"/>
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
@@ -2568,19 +2702,19 @@
     </row>
     <row r="13" spans="1:39" ht="46.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="141"/>
-      <c r="C13" s="143"/>
-      <c r="D13" s="143"/>
-      <c r="E13" s="143"/>
-      <c r="F13" s="143"/>
-      <c r="G13" s="145"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="145"/>
-      <c r="K13" s="145"/>
-      <c r="L13" s="149"/>
-      <c r="M13" s="129"/>
-      <c r="N13" s="147"/>
+      <c r="B13" s="144"/>
+      <c r="C13" s="146"/>
+      <c r="D13" s="146"/>
+      <c r="E13" s="146"/>
+      <c r="F13" s="146"/>
+      <c r="G13" s="148"/>
+      <c r="H13" s="150"/>
+      <c r="I13" s="150"/>
+      <c r="J13" s="148"/>
+      <c r="K13" s="148"/>
+      <c r="L13" s="154"/>
+      <c r="M13" s="156"/>
+      <c r="N13" s="152"/>
       <c r="O13" s="59" t="s">
         <v>22</v>
       </c>
@@ -2608,9 +2742,15 @@
       <c r="W13" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
-      <c r="Z13" s="1"/>
+      <c r="X13" s="137" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y13" s="137" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z13" s="137" t="s">
+        <v>37</v>
+      </c>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
@@ -2649,9 +2789,9 @@
       <c r="U14" s="93"/>
       <c r="V14" s="70"/>
       <c r="W14" s="103"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
+      <c r="X14" s="128"/>
+      <c r="Y14" s="129"/>
+      <c r="Z14" s="130"/>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
@@ -2674,9 +2814,18 @@
       <c r="E15" s="67"/>
       <c r="F15" s="66"/>
       <c r="G15" s="74"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73"/>
+      <c r="H15" s="162">
+        <f>$H$12</f>
+        <v>0.05</v>
+      </c>
+      <c r="I15" s="73">
+        <f>F15*H15</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="73">
+        <f>I15*E15</f>
+        <v>0</v>
+      </c>
       <c r="K15" s="68"/>
       <c r="L15" s="73"/>
       <c r="M15" s="73">
@@ -2705,9 +2854,9 @@
         <v>0</v>
       </c>
       <c r="W15" s="105"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-      <c r="Z15" s="1"/>
+      <c r="X15" s="131"/>
+      <c r="Y15" s="132"/>
+      <c r="Z15" s="133"/>
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
@@ -2730,13 +2879,22 @@
       <c r="E16" s="67"/>
       <c r="F16" s="66"/>
       <c r="G16" s="74"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="73"/>
-      <c r="J16" s="73"/>
+      <c r="H16" s="162">
+        <f t="shared" ref="H16:H79" si="0">$H$12</f>
+        <v>0.05</v>
+      </c>
+      <c r="I16" s="73">
+        <f t="shared" ref="I16:I79" si="1">F16*H16</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="73">
+        <f t="shared" ref="J16:J79" si="2">I16*E16</f>
+        <v>0</v>
+      </c>
       <c r="K16" s="68"/>
       <c r="L16" s="73"/>
       <c r="M16" s="73">
-        <f t="shared" ref="M16:M78" si="0">K16*L16</f>
+        <f t="shared" ref="M16:M78" si="3">K16*L16</f>
         <v>0</v>
       </c>
       <c r="N16" s="78">
@@ -2745,7 +2903,7 @@
       </c>
       <c r="O16" s="90"/>
       <c r="P16" s="73">
-        <f t="shared" ref="P16:P78" si="1">N16*O16</f>
+        <f t="shared" ref="P16:P78" si="4">N16*O16</f>
         <v>0</v>
       </c>
       <c r="Q16" s="91"/>
@@ -2757,13 +2915,13 @@
       <c r="T16" s="76"/>
       <c r="U16" s="94"/>
       <c r="V16" s="75">
-        <f t="shared" ref="V16:V78" si="2">N16*U16</f>
+        <f t="shared" ref="V16:V78" si="5">N16*U16</f>
         <v>0</v>
       </c>
       <c r="W16" s="105"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
+      <c r="X16" s="131"/>
+      <c r="Y16" s="132"/>
+      <c r="Z16" s="133"/>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
@@ -2786,40 +2944,49 @@
       <c r="E17" s="67"/>
       <c r="F17" s="66"/>
       <c r="G17" s="74"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="73"/>
+      <c r="H17" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I17" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="68"/>
       <c r="L17" s="73"/>
       <c r="M17" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N17" s="78">
-        <f t="shared" ref="N17:N78" si="3">E17-K17</f>
+        <f t="shared" ref="N17:N78" si="6">E17-K17</f>
         <v>0</v>
       </c>
       <c r="O17" s="90"/>
       <c r="P17" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q17" s="91"/>
       <c r="R17" s="96"/>
       <c r="S17" s="65">
-        <f t="shared" ref="S17:S78" si="4">N17*R17</f>
+        <f t="shared" ref="S17:S78" si="7">N17*R17</f>
         <v>0</v>
       </c>
       <c r="T17" s="76"/>
       <c r="U17" s="94"/>
       <c r="V17" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W17" s="105"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-      <c r="Z17" s="1"/>
+      <c r="X17" s="131"/>
+      <c r="Y17" s="132"/>
+      <c r="Z17" s="133"/>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
@@ -2842,40 +3009,49 @@
       <c r="E18" s="67"/>
       <c r="F18" s="66"/>
       <c r="G18" s="74"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="73"/>
-      <c r="J18" s="73"/>
+      <c r="H18" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I18" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K18" s="68"/>
       <c r="L18" s="73"/>
       <c r="M18" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N18" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O18" s="90"/>
       <c r="P18" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q18" s="91"/>
       <c r="R18" s="96"/>
       <c r="S18" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T18" s="76"/>
       <c r="U18" s="94"/>
       <c r="V18" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W18" s="105"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-      <c r="Z18" s="1"/>
+      <c r="X18" s="131"/>
+      <c r="Y18" s="132"/>
+      <c r="Z18" s="133"/>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
@@ -2898,40 +3074,49 @@
       <c r="E19" s="67"/>
       <c r="F19" s="66"/>
       <c r="G19" s="74"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="73"/>
+      <c r="H19" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I19" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K19" s="68"/>
       <c r="L19" s="73"/>
       <c r="M19" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N19" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O19" s="90"/>
       <c r="P19" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q19" s="91"/>
       <c r="R19" s="96"/>
       <c r="S19" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T19" s="76"/>
       <c r="U19" s="94"/>
       <c r="V19" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W19" s="105"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-      <c r="Z19" s="1"/>
+      <c r="X19" s="131"/>
+      <c r="Y19" s="132"/>
+      <c r="Z19" s="133"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
@@ -2954,40 +3139,49 @@
       <c r="E20" s="67"/>
       <c r="F20" s="66"/>
       <c r="G20" s="74"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="73"/>
+      <c r="H20" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I20" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K20" s="68"/>
       <c r="L20" s="73"/>
       <c r="M20" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N20" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O20" s="90"/>
       <c r="P20" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q20" s="91"/>
       <c r="R20" s="96"/>
       <c r="S20" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T20" s="76"/>
       <c r="U20" s="94"/>
       <c r="V20" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W20" s="105"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
+      <c r="X20" s="131"/>
+      <c r="Y20" s="132"/>
+      <c r="Z20" s="133"/>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
@@ -3010,40 +3204,49 @@
       <c r="E21" s="67"/>
       <c r="F21" s="66"/>
       <c r="G21" s="74"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="73"/>
-      <c r="J21" s="73"/>
+      <c r="H21" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I21" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K21" s="68"/>
       <c r="L21" s="73"/>
       <c r="M21" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N21" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O21" s="90"/>
       <c r="P21" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q21" s="91"/>
       <c r="R21" s="96"/>
       <c r="S21" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T21" s="76"/>
       <c r="U21" s="94"/>
       <c r="V21" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W21" s="105"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
+      <c r="X21" s="131"/>
+      <c r="Y21" s="132"/>
+      <c r="Z21" s="133"/>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
@@ -3066,40 +3269,49 @@
       <c r="E22" s="67"/>
       <c r="F22" s="66"/>
       <c r="G22" s="74"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
+      <c r="H22" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I22" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K22" s="68"/>
       <c r="L22" s="73"/>
       <c r="M22" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N22" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O22" s="90"/>
       <c r="P22" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q22" s="91"/>
       <c r="R22" s="96"/>
       <c r="S22" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T22" s="76"/>
       <c r="U22" s="94"/>
       <c r="V22" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W22" s="105"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
+      <c r="X22" s="131"/>
+      <c r="Y22" s="132"/>
+      <c r="Z22" s="133"/>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
@@ -3122,40 +3334,49 @@
       <c r="E23" s="67"/>
       <c r="F23" s="66"/>
       <c r="G23" s="74"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="73"/>
+      <c r="H23" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I23" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K23" s="68"/>
       <c r="L23" s="73"/>
       <c r="M23" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N23" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O23" s="90"/>
       <c r="P23" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q23" s="91"/>
       <c r="R23" s="96"/>
       <c r="S23" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T23" s="76"/>
       <c r="U23" s="94"/>
       <c r="V23" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W23" s="105"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-      <c r="Z23" s="1"/>
+      <c r="X23" s="131"/>
+      <c r="Y23" s="132"/>
+      <c r="Z23" s="133"/>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
@@ -3178,40 +3399,49 @@
       <c r="E24" s="67"/>
       <c r="F24" s="66"/>
       <c r="G24" s="74"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73"/>
-      <c r="J24" s="73"/>
+      <c r="H24" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I24" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K24" s="68"/>
       <c r="L24" s="73"/>
       <c r="M24" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N24" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O24" s="90"/>
       <c r="P24" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q24" s="91"/>
       <c r="R24" s="96"/>
       <c r="S24" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T24" s="76"/>
       <c r="U24" s="94"/>
       <c r="V24" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W24" s="105"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-      <c r="Z24" s="1"/>
+      <c r="X24" s="131"/>
+      <c r="Y24" s="132"/>
+      <c r="Z24" s="133"/>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
@@ -3234,40 +3464,49 @@
       <c r="E25" s="67"/>
       <c r="F25" s="66"/>
       <c r="G25" s="74"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="73"/>
-      <c r="J25" s="73"/>
+      <c r="H25" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I25" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K25" s="68"/>
       <c r="L25" s="73"/>
       <c r="M25" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N25" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O25" s="90"/>
       <c r="P25" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q25" s="91"/>
       <c r="R25" s="96"/>
       <c r="S25" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T25" s="76"/>
       <c r="U25" s="94"/>
       <c r="V25" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W25" s="105"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
+      <c r="X25" s="131"/>
+      <c r="Y25" s="132"/>
+      <c r="Z25" s="133"/>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
@@ -3290,40 +3529,49 @@
       <c r="E26" s="67"/>
       <c r="F26" s="66"/>
       <c r="G26" s="74"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="73"/>
+      <c r="H26" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I26" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K26" s="68"/>
       <c r="L26" s="73"/>
       <c r="M26" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N26" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O26" s="90"/>
       <c r="P26" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q26" s="91"/>
       <c r="R26" s="96"/>
       <c r="S26" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T26" s="76"/>
       <c r="U26" s="94"/>
       <c r="V26" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W26" s="105"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-      <c r="Z26" s="1"/>
+      <c r="X26" s="131"/>
+      <c r="Y26" s="132"/>
+      <c r="Z26" s="133"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
@@ -3346,40 +3594,49 @@
       <c r="E27" s="67"/>
       <c r="F27" s="66"/>
       <c r="G27" s="74"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="73"/>
-      <c r="J27" s="73"/>
+      <c r="H27" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I27" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K27" s="68"/>
       <c r="L27" s="73"/>
       <c r="M27" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N27" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O27" s="90"/>
       <c r="P27" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q27" s="91"/>
       <c r="R27" s="96"/>
       <c r="S27" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T27" s="76"/>
       <c r="U27" s="94"/>
       <c r="V27" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W27" s="105"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
+      <c r="X27" s="131"/>
+      <c r="Y27" s="132"/>
+      <c r="Z27" s="133"/>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
@@ -3402,40 +3659,49 @@
       <c r="E28" s="67"/>
       <c r="F28" s="66"/>
       <c r="G28" s="74"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="73"/>
-      <c r="J28" s="73"/>
+      <c r="H28" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I28" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K28" s="68"/>
       <c r="L28" s="73"/>
       <c r="M28" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N28" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O28" s="90"/>
       <c r="P28" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q28" s="91"/>
       <c r="R28" s="96"/>
       <c r="S28" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T28" s="76"/>
       <c r="U28" s="94"/>
       <c r="V28" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W28" s="105"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
+      <c r="X28" s="131"/>
+      <c r="Y28" s="132"/>
+      <c r="Z28" s="133"/>
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
@@ -3458,40 +3724,49 @@
       <c r="E29" s="67"/>
       <c r="F29" s="66"/>
       <c r="G29" s="74"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="73"/>
+      <c r="H29" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I29" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K29" s="68"/>
       <c r="L29" s="73"/>
       <c r="M29" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N29" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O29" s="90"/>
       <c r="P29" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q29" s="91"/>
       <c r="R29" s="96"/>
       <c r="S29" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T29" s="76"/>
       <c r="U29" s="94"/>
       <c r="V29" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W29" s="105"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
+      <c r="X29" s="131"/>
+      <c r="Y29" s="132"/>
+      <c r="Z29" s="133"/>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
@@ -3514,40 +3789,49 @@
       <c r="E30" s="67"/>
       <c r="F30" s="66"/>
       <c r="G30" s="74"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
+      <c r="H30" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I30" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K30" s="68"/>
       <c r="L30" s="73"/>
       <c r="M30" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N30" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O30" s="90"/>
       <c r="P30" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q30" s="91"/>
       <c r="R30" s="96"/>
       <c r="S30" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T30" s="76"/>
       <c r="U30" s="94"/>
       <c r="V30" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W30" s="105"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
+      <c r="X30" s="131"/>
+      <c r="Y30" s="132"/>
+      <c r="Z30" s="133"/>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
@@ -3570,40 +3854,49 @@
       <c r="E31" s="67"/>
       <c r="F31" s="66"/>
       <c r="G31" s="74"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="73"/>
-      <c r="J31" s="73"/>
+      <c r="H31" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I31" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K31" s="68"/>
       <c r="L31" s="73"/>
       <c r="M31" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N31" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O31" s="90"/>
       <c r="P31" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q31" s="91"/>
       <c r="R31" s="96"/>
       <c r="S31" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T31" s="76"/>
       <c r="U31" s="94"/>
       <c r="V31" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W31" s="105"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
+      <c r="X31" s="131"/>
+      <c r="Y31" s="132"/>
+      <c r="Z31" s="133"/>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
@@ -3626,40 +3919,49 @@
       <c r="E32" s="67"/>
       <c r="F32" s="66"/>
       <c r="G32" s="74"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
-      <c r="J32" s="73"/>
+      <c r="H32" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I32" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K32" s="68"/>
       <c r="L32" s="73"/>
       <c r="M32" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N32" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O32" s="90"/>
       <c r="P32" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q32" s="91"/>
       <c r="R32" s="96"/>
       <c r="S32" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T32" s="76"/>
       <c r="U32" s="94"/>
       <c r="V32" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W32" s="105"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
+      <c r="X32" s="131"/>
+      <c r="Y32" s="132"/>
+      <c r="Z32" s="133"/>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
@@ -3682,40 +3984,49 @@
       <c r="E33" s="67"/>
       <c r="F33" s="66"/>
       <c r="G33" s="74"/>
-      <c r="H33" s="73"/>
-      <c r="I33" s="73"/>
-      <c r="J33" s="73"/>
+      <c r="H33" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I33" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K33" s="68"/>
       <c r="L33" s="73"/>
       <c r="M33" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N33" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O33" s="90"/>
       <c r="P33" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q33" s="91"/>
       <c r="R33" s="96"/>
       <c r="S33" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T33" s="76"/>
       <c r="U33" s="94"/>
       <c r="V33" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W33" s="105"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
-      <c r="Z33" s="1"/>
+      <c r="X33" s="131"/>
+      <c r="Y33" s="132"/>
+      <c r="Z33" s="133"/>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
@@ -3738,40 +4049,49 @@
       <c r="E34" s="67"/>
       <c r="F34" s="66"/>
       <c r="G34" s="74"/>
-      <c r="H34" s="73"/>
-      <c r="I34" s="73"/>
-      <c r="J34" s="73"/>
+      <c r="H34" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I34" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K34" s="68"/>
       <c r="L34" s="73"/>
       <c r="M34" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N34" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O34" s="90"/>
       <c r="P34" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q34" s="91"/>
       <c r="R34" s="96"/>
       <c r="S34" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T34" s="76"/>
       <c r="U34" s="94"/>
       <c r="V34" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W34" s="105"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-      <c r="Z34" s="1"/>
+      <c r="X34" s="131"/>
+      <c r="Y34" s="132"/>
+      <c r="Z34" s="133"/>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
@@ -3794,40 +4114,49 @@
       <c r="E35" s="67"/>
       <c r="F35" s="66"/>
       <c r="G35" s="74"/>
-      <c r="H35" s="73"/>
-      <c r="I35" s="73"/>
-      <c r="J35" s="73"/>
+      <c r="H35" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I35" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K35" s="68"/>
       <c r="L35" s="73"/>
       <c r="M35" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N35" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O35" s="90"/>
       <c r="P35" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q35" s="91"/>
       <c r="R35" s="96"/>
       <c r="S35" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T35" s="76"/>
       <c r="U35" s="94"/>
       <c r="V35" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W35" s="105"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
+      <c r="X35" s="131"/>
+      <c r="Y35" s="132"/>
+      <c r="Z35" s="133"/>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
@@ -3850,40 +4179,49 @@
       <c r="E36" s="67"/>
       <c r="F36" s="66"/>
       <c r="G36" s="74"/>
-      <c r="H36" s="73"/>
-      <c r="I36" s="73"/>
-      <c r="J36" s="73"/>
+      <c r="H36" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I36" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K36" s="68"/>
       <c r="L36" s="73"/>
       <c r="M36" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N36" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O36" s="90"/>
       <c r="P36" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q36" s="91"/>
       <c r="R36" s="96"/>
       <c r="S36" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T36" s="76"/>
       <c r="U36" s="94"/>
       <c r="V36" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W36" s="105"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
+      <c r="X36" s="131"/>
+      <c r="Y36" s="132"/>
+      <c r="Z36" s="133"/>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
@@ -3906,40 +4244,49 @@
       <c r="E37" s="67"/>
       <c r="F37" s="66"/>
       <c r="G37" s="74"/>
-      <c r="H37" s="73"/>
-      <c r="I37" s="73"/>
-      <c r="J37" s="73"/>
+      <c r="H37" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I37" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K37" s="68"/>
       <c r="L37" s="73"/>
       <c r="M37" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N37" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O37" s="90"/>
       <c r="P37" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q37" s="91"/>
       <c r="R37" s="96"/>
       <c r="S37" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T37" s="76"/>
       <c r="U37" s="94"/>
       <c r="V37" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W37" s="105"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
+      <c r="X37" s="131"/>
+      <c r="Y37" s="132"/>
+      <c r="Z37" s="133"/>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
@@ -3962,40 +4309,49 @@
       <c r="E38" s="67"/>
       <c r="F38" s="66"/>
       <c r="G38" s="74"/>
-      <c r="H38" s="73"/>
-      <c r="I38" s="73"/>
-      <c r="J38" s="73"/>
+      <c r="H38" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I38" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K38" s="68"/>
       <c r="L38" s="73"/>
       <c r="M38" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N38" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O38" s="90"/>
       <c r="P38" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q38" s="91"/>
       <c r="R38" s="96"/>
       <c r="S38" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T38" s="76"/>
       <c r="U38" s="94"/>
       <c r="V38" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W38" s="105"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
+      <c r="X38" s="131"/>
+      <c r="Y38" s="132"/>
+      <c r="Z38" s="133"/>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
@@ -4018,40 +4374,49 @@
       <c r="E39" s="121"/>
       <c r="F39" s="66"/>
       <c r="G39" s="74"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="73"/>
-      <c r="J39" s="73"/>
+      <c r="H39" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I39" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K39" s="68"/>
       <c r="L39" s="73"/>
       <c r="M39" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N39" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O39" s="90"/>
       <c r="P39" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q39" s="91"/>
       <c r="R39" s="96"/>
       <c r="S39" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T39" s="76"/>
       <c r="U39" s="94"/>
       <c r="V39" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W39" s="105"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
+      <c r="X39" s="131"/>
+      <c r="Y39" s="132"/>
+      <c r="Z39" s="133"/>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
@@ -4074,40 +4439,49 @@
       <c r="E40" s="121"/>
       <c r="F40" s="66"/>
       <c r="G40" s="74"/>
-      <c r="H40" s="73"/>
-      <c r="I40" s="73"/>
-      <c r="J40" s="73"/>
+      <c r="H40" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I40" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K40" s="68"/>
       <c r="L40" s="73"/>
       <c r="M40" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N40" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O40" s="90"/>
       <c r="P40" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q40" s="91"/>
       <c r="R40" s="96"/>
       <c r="S40" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T40" s="76"/>
       <c r="U40" s="94"/>
       <c r="V40" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W40" s="105"/>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
-      <c r="Z40" s="1"/>
+      <c r="X40" s="131"/>
+      <c r="Y40" s="132"/>
+      <c r="Z40" s="133"/>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
@@ -4130,40 +4504,49 @@
       <c r="E41" s="121"/>
       <c r="F41" s="66"/>
       <c r="G41" s="74"/>
-      <c r="H41" s="73"/>
-      <c r="I41" s="73"/>
-      <c r="J41" s="73"/>
+      <c r="H41" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I41" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K41" s="68"/>
       <c r="L41" s="73"/>
       <c r="M41" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N41" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O41" s="90"/>
       <c r="P41" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q41" s="91"/>
       <c r="R41" s="96"/>
       <c r="S41" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T41" s="76"/>
       <c r="U41" s="94"/>
       <c r="V41" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W41" s="105"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
-      <c r="Z41" s="1"/>
+      <c r="X41" s="131"/>
+      <c r="Y41" s="132"/>
+      <c r="Z41" s="133"/>
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
@@ -4186,40 +4569,49 @@
       <c r="E42" s="121"/>
       <c r="F42" s="66"/>
       <c r="G42" s="74"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="73"/>
-      <c r="J42" s="73"/>
+      <c r="H42" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I42" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K42" s="68"/>
       <c r="L42" s="73"/>
       <c r="M42" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N42" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O42" s="90"/>
       <c r="P42" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q42" s="91"/>
       <c r="R42" s="96"/>
       <c r="S42" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T42" s="76"/>
       <c r="U42" s="94"/>
       <c r="V42" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W42" s="105"/>
-      <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
+      <c r="X42" s="131"/>
+      <c r="Y42" s="132"/>
+      <c r="Z42" s="133"/>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
@@ -4242,40 +4634,49 @@
       <c r="E43" s="121"/>
       <c r="F43" s="66"/>
       <c r="G43" s="74"/>
-      <c r="H43" s="73"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="73"/>
+      <c r="H43" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I43" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K43" s="68"/>
       <c r="L43" s="73"/>
       <c r="M43" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N43" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O43" s="90"/>
       <c r="P43" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q43" s="91"/>
       <c r="R43" s="96"/>
       <c r="S43" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T43" s="76"/>
       <c r="U43" s="94"/>
       <c r="V43" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W43" s="105"/>
-      <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
-      <c r="Z43" s="1"/>
+      <c r="X43" s="131"/>
+      <c r="Y43" s="132"/>
+      <c r="Z43" s="133"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
@@ -4298,40 +4699,49 @@
       <c r="E44" s="67"/>
       <c r="F44" s="66"/>
       <c r="G44" s="74"/>
-      <c r="H44" s="73"/>
-      <c r="I44" s="73"/>
-      <c r="J44" s="73"/>
+      <c r="H44" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I44" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K44" s="68"/>
       <c r="L44" s="73"/>
       <c r="M44" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N44" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O44" s="90"/>
       <c r="P44" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q44" s="91"/>
       <c r="R44" s="96"/>
       <c r="S44" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T44" s="76"/>
       <c r="U44" s="94"/>
       <c r="V44" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W44" s="105"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
+      <c r="X44" s="131"/>
+      <c r="Y44" s="132"/>
+      <c r="Z44" s="133"/>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
@@ -4354,40 +4764,49 @@
       <c r="E45" s="67"/>
       <c r="F45" s="66"/>
       <c r="G45" s="74"/>
-      <c r="H45" s="73"/>
-      <c r="I45" s="73"/>
-      <c r="J45" s="73"/>
+      <c r="H45" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I45" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K45" s="68"/>
       <c r="L45" s="73"/>
       <c r="M45" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N45" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O45" s="90"/>
       <c r="P45" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q45" s="91"/>
       <c r="R45" s="96"/>
       <c r="S45" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T45" s="76"/>
       <c r="U45" s="94"/>
       <c r="V45" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W45" s="105"/>
-      <c r="X45" s="1"/>
-      <c r="Y45" s="1"/>
-      <c r="Z45" s="1"/>
+      <c r="X45" s="131"/>
+      <c r="Y45" s="132"/>
+      <c r="Z45" s="133"/>
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
@@ -4410,40 +4829,49 @@
       <c r="E46" s="67"/>
       <c r="F46" s="66"/>
       <c r="G46" s="74"/>
-      <c r="H46" s="73"/>
-      <c r="I46" s="73"/>
-      <c r="J46" s="73"/>
+      <c r="H46" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I46" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K46" s="68"/>
       <c r="L46" s="73"/>
       <c r="M46" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N46" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O46" s="90"/>
       <c r="P46" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q46" s="91"/>
       <c r="R46" s="96"/>
       <c r="S46" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T46" s="76"/>
       <c r="U46" s="94"/>
       <c r="V46" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W46" s="105"/>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
+      <c r="X46" s="131"/>
+      <c r="Y46" s="132"/>
+      <c r="Z46" s="133"/>
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
@@ -4466,40 +4894,49 @@
       <c r="E47" s="67"/>
       <c r="F47" s="66"/>
       <c r="G47" s="74"/>
-      <c r="H47" s="73"/>
-      <c r="I47" s="73"/>
-      <c r="J47" s="73"/>
+      <c r="H47" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I47" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K47" s="68"/>
       <c r="L47" s="73"/>
       <c r="M47" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N47" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O47" s="90"/>
       <c r="P47" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q47" s="91"/>
       <c r="R47" s="96"/>
       <c r="S47" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T47" s="76"/>
       <c r="U47" s="94"/>
       <c r="V47" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W47" s="105"/>
-      <c r="X47" s="1"/>
-      <c r="Y47" s="1"/>
-      <c r="Z47" s="1"/>
+      <c r="X47" s="131"/>
+      <c r="Y47" s="132"/>
+      <c r="Z47" s="133"/>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
@@ -4522,40 +4959,49 @@
       <c r="E48" s="67"/>
       <c r="F48" s="66"/>
       <c r="G48" s="74"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="73"/>
-      <c r="J48" s="73"/>
+      <c r="H48" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I48" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K48" s="68"/>
       <c r="L48" s="73"/>
       <c r="M48" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N48" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O48" s="90"/>
       <c r="P48" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q48" s="91"/>
       <c r="R48" s="96"/>
       <c r="S48" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T48" s="76"/>
       <c r="U48" s="94"/>
       <c r="V48" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W48" s="105"/>
-      <c r="X48" s="1"/>
-      <c r="Y48" s="1"/>
-      <c r="Z48" s="1"/>
+      <c r="X48" s="131"/>
+      <c r="Y48" s="132"/>
+      <c r="Z48" s="133"/>
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
@@ -4578,40 +5024,49 @@
       <c r="E49" s="67"/>
       <c r="F49" s="66"/>
       <c r="G49" s="74"/>
-      <c r="H49" s="73"/>
-      <c r="I49" s="73"/>
-      <c r="J49" s="73"/>
+      <c r="H49" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I49" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K49" s="68"/>
       <c r="L49" s="73"/>
       <c r="M49" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N49" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O49" s="90"/>
       <c r="P49" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q49" s="91"/>
       <c r="R49" s="96"/>
       <c r="S49" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T49" s="76"/>
       <c r="U49" s="94"/>
       <c r="V49" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W49" s="105"/>
-      <c r="X49" s="1"/>
-      <c r="Y49" s="1"/>
-      <c r="Z49" s="1"/>
+      <c r="X49" s="131"/>
+      <c r="Y49" s="132"/>
+      <c r="Z49" s="133"/>
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
@@ -4634,40 +5089,49 @@
       <c r="E50" s="67"/>
       <c r="F50" s="66"/>
       <c r="G50" s="74"/>
-      <c r="H50" s="73"/>
-      <c r="I50" s="73"/>
-      <c r="J50" s="73"/>
+      <c r="H50" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I50" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K50" s="68"/>
       <c r="L50" s="73"/>
       <c r="M50" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N50" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O50" s="124"/>
       <c r="P50" s="125">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q50" s="126"/>
       <c r="R50" s="96"/>
       <c r="S50" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T50" s="76"/>
       <c r="U50" s="94"/>
       <c r="V50" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W50" s="105"/>
-      <c r="X50" s="1"/>
-      <c r="Y50" s="1"/>
-      <c r="Z50" s="1"/>
+      <c r="X50" s="131"/>
+      <c r="Y50" s="132"/>
+      <c r="Z50" s="133"/>
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
@@ -4690,40 +5154,49 @@
       <c r="E51" s="67"/>
       <c r="F51" s="66"/>
       <c r="G51" s="74"/>
-      <c r="H51" s="73"/>
-      <c r="I51" s="73"/>
-      <c r="J51" s="73"/>
+      <c r="H51" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I51" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K51" s="68"/>
       <c r="L51" s="73"/>
       <c r="M51" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N51" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O51" s="90"/>
       <c r="P51" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q51" s="91"/>
       <c r="R51" s="96"/>
       <c r="S51" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T51" s="76"/>
       <c r="U51" s="94"/>
       <c r="V51" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W51" s="105"/>
-      <c r="X51" s="1"/>
-      <c r="Y51" s="1"/>
-      <c r="Z51" s="1"/>
+      <c r="X51" s="131"/>
+      <c r="Y51" s="132"/>
+      <c r="Z51" s="133"/>
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
@@ -4746,40 +5219,49 @@
       <c r="E52" s="67"/>
       <c r="F52" s="66"/>
       <c r="G52" s="74"/>
-      <c r="H52" s="73"/>
-      <c r="I52" s="73"/>
-      <c r="J52" s="73"/>
+      <c r="H52" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I52" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K52" s="68"/>
       <c r="L52" s="73"/>
       <c r="M52" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N52" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O52" s="90"/>
       <c r="P52" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q52" s="91"/>
       <c r="R52" s="96"/>
       <c r="S52" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T52" s="76"/>
       <c r="U52" s="94"/>
       <c r="V52" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W52" s="105"/>
-      <c r="X52" s="1"/>
-      <c r="Y52" s="1"/>
-      <c r="Z52" s="1"/>
+      <c r="X52" s="131"/>
+      <c r="Y52" s="132"/>
+      <c r="Z52" s="133"/>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
@@ -4802,40 +5284,49 @@
       <c r="E53" s="67"/>
       <c r="F53" s="66"/>
       <c r="G53" s="74"/>
-      <c r="H53" s="73"/>
-      <c r="I53" s="73"/>
-      <c r="J53" s="73"/>
+      <c r="H53" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I53" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K53" s="68"/>
       <c r="L53" s="73"/>
       <c r="M53" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N53" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O53" s="90"/>
       <c r="P53" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q53" s="91"/>
       <c r="R53" s="96"/>
       <c r="S53" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T53" s="76"/>
       <c r="U53" s="94"/>
       <c r="V53" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W53" s="105"/>
-      <c r="X53" s="1"/>
-      <c r="Y53" s="1"/>
-      <c r="Z53" s="1"/>
+      <c r="X53" s="131"/>
+      <c r="Y53" s="132"/>
+      <c r="Z53" s="133"/>
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
@@ -4858,40 +5349,49 @@
       <c r="E54" s="67"/>
       <c r="F54" s="66"/>
       <c r="G54" s="74"/>
-      <c r="H54" s="73"/>
-      <c r="I54" s="73"/>
-      <c r="J54" s="73"/>
+      <c r="H54" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I54" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K54" s="68"/>
       <c r="L54" s="73"/>
       <c r="M54" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N54" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O54" s="90"/>
       <c r="P54" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q54" s="91"/>
       <c r="R54" s="96"/>
       <c r="S54" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T54" s="76"/>
       <c r="U54" s="94"/>
       <c r="V54" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W54" s="105"/>
-      <c r="X54" s="1"/>
-      <c r="Y54" s="1"/>
-      <c r="Z54" s="1"/>
+      <c r="X54" s="131"/>
+      <c r="Y54" s="132"/>
+      <c r="Z54" s="133"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
@@ -4914,40 +5414,49 @@
       <c r="E55" s="67"/>
       <c r="F55" s="66"/>
       <c r="G55" s="74"/>
-      <c r="H55" s="73"/>
-      <c r="I55" s="73"/>
-      <c r="J55" s="73"/>
+      <c r="H55" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I55" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K55" s="68"/>
       <c r="L55" s="73"/>
       <c r="M55" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N55" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O55" s="90"/>
       <c r="P55" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q55" s="91"/>
       <c r="R55" s="96"/>
       <c r="S55" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T55" s="76"/>
       <c r="U55" s="94"/>
       <c r="V55" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W55" s="105"/>
-      <c r="X55" s="1"/>
-      <c r="Y55" s="1"/>
-      <c r="Z55" s="1"/>
+      <c r="X55" s="131"/>
+      <c r="Y55" s="132"/>
+      <c r="Z55" s="133"/>
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
@@ -4970,40 +5479,49 @@
       <c r="E56" s="67"/>
       <c r="F56" s="66"/>
       <c r="G56" s="74"/>
-      <c r="H56" s="73"/>
-      <c r="I56" s="73"/>
-      <c r="J56" s="73"/>
+      <c r="H56" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I56" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K56" s="68"/>
       <c r="L56" s="73"/>
       <c r="M56" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N56" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O56" s="90"/>
       <c r="P56" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q56" s="91"/>
       <c r="R56" s="96"/>
       <c r="S56" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T56" s="76"/>
       <c r="U56" s="94"/>
       <c r="V56" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W56" s="105"/>
-      <c r="X56" s="1"/>
-      <c r="Y56" s="1"/>
-      <c r="Z56" s="1"/>
+      <c r="X56" s="131"/>
+      <c r="Y56" s="132"/>
+      <c r="Z56" s="133"/>
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
@@ -5026,40 +5544,49 @@
       <c r="E57" s="67"/>
       <c r="F57" s="66"/>
       <c r="G57" s="74"/>
-      <c r="H57" s="73"/>
-      <c r="I57" s="73"/>
-      <c r="J57" s="73"/>
+      <c r="H57" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I57" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K57" s="68"/>
       <c r="L57" s="73"/>
       <c r="M57" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N57" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O57" s="90"/>
       <c r="P57" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q57" s="91"/>
       <c r="R57" s="96"/>
       <c r="S57" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T57" s="76"/>
       <c r="U57" s="94"/>
       <c r="V57" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W57" s="105"/>
-      <c r="X57" s="1"/>
-      <c r="Y57" s="1"/>
-      <c r="Z57" s="1"/>
+      <c r="X57" s="131"/>
+      <c r="Y57" s="132"/>
+      <c r="Z57" s="133"/>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
@@ -5082,40 +5609,49 @@
       <c r="E58" s="67"/>
       <c r="F58" s="66"/>
       <c r="G58" s="74"/>
-      <c r="H58" s="73"/>
-      <c r="I58" s="73"/>
-      <c r="J58" s="73"/>
+      <c r="H58" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I58" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K58" s="68"/>
       <c r="L58" s="73"/>
       <c r="M58" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N58" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O58" s="90"/>
       <c r="P58" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q58" s="91"/>
       <c r="R58" s="96"/>
       <c r="S58" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T58" s="76"/>
       <c r="U58" s="94"/>
       <c r="V58" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W58" s="105"/>
-      <c r="X58" s="1"/>
-      <c r="Y58" s="1"/>
-      <c r="Z58" s="1"/>
+      <c r="X58" s="131"/>
+      <c r="Y58" s="132"/>
+      <c r="Z58" s="133"/>
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
@@ -5138,40 +5674,49 @@
       <c r="E59" s="67"/>
       <c r="F59" s="66"/>
       <c r="G59" s="74"/>
-      <c r="H59" s="73"/>
-      <c r="I59" s="73"/>
-      <c r="J59" s="73"/>
+      <c r="H59" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I59" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K59" s="68"/>
       <c r="L59" s="73"/>
       <c r="M59" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N59" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O59" s="90"/>
       <c r="P59" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q59" s="91"/>
       <c r="R59" s="96"/>
       <c r="S59" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T59" s="76"/>
       <c r="U59" s="94"/>
       <c r="V59" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W59" s="105"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="1"/>
-      <c r="Z59" s="1"/>
+      <c r="X59" s="131"/>
+      <c r="Y59" s="132"/>
+      <c r="Z59" s="133"/>
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
@@ -5194,40 +5739,49 @@
       <c r="E60" s="67"/>
       <c r="F60" s="66"/>
       <c r="G60" s="74"/>
-      <c r="H60" s="73"/>
-      <c r="I60" s="73"/>
-      <c r="J60" s="73"/>
+      <c r="H60" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I60" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K60" s="68"/>
       <c r="L60" s="73"/>
       <c r="M60" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N60" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O60" s="90"/>
       <c r="P60" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q60" s="91"/>
       <c r="R60" s="96"/>
       <c r="S60" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T60" s="76"/>
       <c r="U60" s="94"/>
       <c r="V60" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W60" s="105"/>
-      <c r="X60" s="1"/>
-      <c r="Y60" s="1"/>
-      <c r="Z60" s="1"/>
+      <c r="X60" s="131"/>
+      <c r="Y60" s="132"/>
+      <c r="Z60" s="133"/>
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
@@ -5250,40 +5804,49 @@
       <c r="E61" s="67"/>
       <c r="F61" s="66"/>
       <c r="G61" s="74"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
-      <c r="J61" s="73"/>
+      <c r="H61" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I61" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K61" s="68"/>
       <c r="L61" s="73"/>
       <c r="M61" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N61" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O61" s="90"/>
       <c r="P61" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q61" s="91"/>
       <c r="R61" s="96"/>
       <c r="S61" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T61" s="76"/>
       <c r="U61" s="94"/>
       <c r="V61" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W61" s="105"/>
-      <c r="X61" s="1"/>
-      <c r="Y61" s="1"/>
-      <c r="Z61" s="1"/>
+      <c r="X61" s="131"/>
+      <c r="Y61" s="132"/>
+      <c r="Z61" s="133"/>
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
@@ -5306,40 +5869,49 @@
       <c r="E62" s="67"/>
       <c r="F62" s="66"/>
       <c r="G62" s="74"/>
-      <c r="H62" s="73"/>
-      <c r="I62" s="73"/>
-      <c r="J62" s="73"/>
+      <c r="H62" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I62" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K62" s="68"/>
       <c r="L62" s="73"/>
       <c r="M62" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N62" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O62" s="90"/>
       <c r="P62" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q62" s="91"/>
       <c r="R62" s="96"/>
       <c r="S62" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T62" s="76"/>
       <c r="U62" s="94"/>
       <c r="V62" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W62" s="105"/>
-      <c r="X62" s="1"/>
-      <c r="Y62" s="1"/>
-      <c r="Z62" s="1"/>
+      <c r="X62" s="131"/>
+      <c r="Y62" s="132"/>
+      <c r="Z62" s="133"/>
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
@@ -5362,40 +5934,49 @@
       <c r="E63" s="67"/>
       <c r="F63" s="66"/>
       <c r="G63" s="74"/>
-      <c r="H63" s="73"/>
-      <c r="I63" s="73"/>
-      <c r="J63" s="73"/>
+      <c r="H63" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I63" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K63" s="68"/>
       <c r="L63" s="73"/>
       <c r="M63" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N63" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O63" s="90"/>
       <c r="P63" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q63" s="91"/>
       <c r="R63" s="96"/>
       <c r="S63" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T63" s="76"/>
       <c r="U63" s="94"/>
       <c r="V63" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W63" s="105"/>
-      <c r="X63" s="1"/>
-      <c r="Y63" s="1"/>
-      <c r="Z63" s="1"/>
+      <c r="X63" s="131"/>
+      <c r="Y63" s="132"/>
+      <c r="Z63" s="133"/>
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
@@ -5418,40 +5999,49 @@
       <c r="E64" s="67"/>
       <c r="F64" s="66"/>
       <c r="G64" s="74"/>
-      <c r="H64" s="73"/>
-      <c r="I64" s="73"/>
-      <c r="J64" s="73"/>
+      <c r="H64" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I64" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K64" s="68"/>
       <c r="L64" s="73"/>
       <c r="M64" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N64" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O64" s="90"/>
       <c r="P64" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q64" s="91"/>
       <c r="R64" s="96"/>
       <c r="S64" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T64" s="76"/>
       <c r="U64" s="94"/>
       <c r="V64" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W64" s="105"/>
-      <c r="X64" s="1"/>
-      <c r="Y64" s="1"/>
-      <c r="Z64" s="1"/>
+      <c r="X64" s="131"/>
+      <c r="Y64" s="132"/>
+      <c r="Z64" s="133"/>
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
@@ -5474,40 +6064,49 @@
       <c r="E65" s="67"/>
       <c r="F65" s="66"/>
       <c r="G65" s="74"/>
-      <c r="H65" s="73"/>
-      <c r="I65" s="73"/>
-      <c r="J65" s="73"/>
+      <c r="H65" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I65" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J65" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K65" s="68"/>
       <c r="L65" s="73"/>
       <c r="M65" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N65" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O65" s="90"/>
       <c r="P65" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q65" s="91"/>
       <c r="R65" s="96"/>
       <c r="S65" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T65" s="76"/>
       <c r="U65" s="94"/>
       <c r="V65" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W65" s="105"/>
-      <c r="X65" s="1"/>
-      <c r="Y65" s="1"/>
-      <c r="Z65" s="1"/>
+      <c r="X65" s="131"/>
+      <c r="Y65" s="132"/>
+      <c r="Z65" s="133"/>
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
@@ -5530,40 +6129,49 @@
       <c r="E66" s="67"/>
       <c r="F66" s="66"/>
       <c r="G66" s="74"/>
-      <c r="H66" s="73"/>
-      <c r="I66" s="73"/>
-      <c r="J66" s="73"/>
+      <c r="H66" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I66" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K66" s="68"/>
       <c r="L66" s="73"/>
       <c r="M66" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N66" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O66" s="90"/>
       <c r="P66" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q66" s="91"/>
       <c r="R66" s="96"/>
       <c r="S66" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T66" s="76"/>
       <c r="U66" s="94"/>
       <c r="V66" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W66" s="105"/>
-      <c r="X66" s="1"/>
-      <c r="Y66" s="1"/>
-      <c r="Z66" s="1"/>
+      <c r="X66" s="131"/>
+      <c r="Y66" s="132"/>
+      <c r="Z66" s="133"/>
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
@@ -5586,40 +6194,49 @@
       <c r="E67" s="67"/>
       <c r="F67" s="66"/>
       <c r="G67" s="74"/>
-      <c r="H67" s="73"/>
-      <c r="I67" s="73"/>
-      <c r="J67" s="73"/>
+      <c r="H67" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I67" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K67" s="68"/>
       <c r="L67" s="73"/>
       <c r="M67" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N67" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O67" s="90"/>
       <c r="P67" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q67" s="91"/>
       <c r="R67" s="96"/>
       <c r="S67" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T67" s="76"/>
       <c r="U67" s="94"/>
       <c r="V67" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W67" s="105"/>
-      <c r="X67" s="1"/>
-      <c r="Y67" s="1"/>
-      <c r="Z67" s="1"/>
+      <c r="X67" s="131"/>
+      <c r="Y67" s="132"/>
+      <c r="Z67" s="133"/>
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
@@ -5642,40 +6259,49 @@
       <c r="E68" s="67"/>
       <c r="F68" s="66"/>
       <c r="G68" s="74"/>
-      <c r="H68" s="73"/>
-      <c r="I68" s="73"/>
-      <c r="J68" s="73"/>
+      <c r="H68" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I68" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J68" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K68" s="68"/>
       <c r="L68" s="73"/>
       <c r="M68" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N68" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O68" s="90"/>
       <c r="P68" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q68" s="91"/>
       <c r="R68" s="96"/>
       <c r="S68" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T68" s="76"/>
       <c r="U68" s="94"/>
       <c r="V68" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W68" s="105"/>
-      <c r="X68" s="1"/>
-      <c r="Y68" s="1"/>
-      <c r="Z68" s="1"/>
+      <c r="X68" s="131"/>
+      <c r="Y68" s="132"/>
+      <c r="Z68" s="133"/>
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
@@ -5698,40 +6324,49 @@
       <c r="E69" s="67"/>
       <c r="F69" s="66"/>
       <c r="G69" s="74"/>
-      <c r="H69" s="73"/>
-      <c r="I69" s="73"/>
-      <c r="J69" s="73"/>
+      <c r="H69" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I69" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K69" s="68"/>
       <c r="L69" s="73"/>
       <c r="M69" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N69" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O69" s="90"/>
       <c r="P69" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q69" s="91"/>
       <c r="R69" s="96"/>
       <c r="S69" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T69" s="76"/>
       <c r="U69" s="94"/>
       <c r="V69" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W69" s="105"/>
-      <c r="X69" s="1"/>
-      <c r="Y69" s="1"/>
-      <c r="Z69" s="1"/>
+      <c r="X69" s="131"/>
+      <c r="Y69" s="132"/>
+      <c r="Z69" s="133"/>
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
@@ -5754,40 +6389,49 @@
       <c r="E70" s="67"/>
       <c r="F70" s="66"/>
       <c r="G70" s="74"/>
-      <c r="H70" s="73"/>
-      <c r="I70" s="73"/>
-      <c r="J70" s="73"/>
+      <c r="H70" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I70" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K70" s="68"/>
       <c r="L70" s="73"/>
       <c r="M70" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N70" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O70" s="90"/>
       <c r="P70" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q70" s="91"/>
       <c r="R70" s="96"/>
       <c r="S70" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T70" s="76"/>
       <c r="U70" s="94"/>
       <c r="V70" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W70" s="105"/>
-      <c r="X70" s="1"/>
-      <c r="Y70" s="1"/>
-      <c r="Z70" s="1"/>
+      <c r="X70" s="131"/>
+      <c r="Y70" s="132"/>
+      <c r="Z70" s="133"/>
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
@@ -5810,40 +6454,49 @@
       <c r="E71" s="67"/>
       <c r="F71" s="66"/>
       <c r="G71" s="74"/>
-      <c r="H71" s="73"/>
-      <c r="I71" s="73"/>
-      <c r="J71" s="73"/>
+      <c r="H71" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I71" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J71" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K71" s="68"/>
       <c r="L71" s="73"/>
       <c r="M71" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N71" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O71" s="90"/>
       <c r="P71" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q71" s="91"/>
       <c r="R71" s="96"/>
       <c r="S71" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T71" s="76"/>
       <c r="U71" s="94"/>
       <c r="V71" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W71" s="105"/>
-      <c r="X71" s="1"/>
-      <c r="Y71" s="1"/>
-      <c r="Z71" s="1"/>
+      <c r="X71" s="131"/>
+      <c r="Y71" s="132"/>
+      <c r="Z71" s="133"/>
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
@@ -5866,40 +6519,49 @@
       <c r="E72" s="67"/>
       <c r="F72" s="66"/>
       <c r="G72" s="74"/>
-      <c r="H72" s="73"/>
-      <c r="I72" s="73"/>
-      <c r="J72" s="73"/>
+      <c r="H72" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I72" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J72" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K72" s="68"/>
       <c r="L72" s="73"/>
       <c r="M72" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N72" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O72" s="90"/>
       <c r="P72" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q72" s="91"/>
       <c r="R72" s="96"/>
       <c r="S72" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T72" s="76"/>
       <c r="U72" s="94"/>
       <c r="V72" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W72" s="105"/>
-      <c r="X72" s="1"/>
-      <c r="Y72" s="1"/>
-      <c r="Z72" s="1"/>
+      <c r="X72" s="131"/>
+      <c r="Y72" s="132"/>
+      <c r="Z72" s="133"/>
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
@@ -5922,40 +6584,49 @@
       <c r="E73" s="67"/>
       <c r="F73" s="66"/>
       <c r="G73" s="74"/>
-      <c r="H73" s="73"/>
-      <c r="I73" s="73"/>
-      <c r="J73" s="73"/>
+      <c r="H73" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I73" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J73" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K73" s="68"/>
       <c r="L73" s="73"/>
       <c r="M73" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N73" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O73" s="90"/>
       <c r="P73" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q73" s="91"/>
       <c r="R73" s="96"/>
       <c r="S73" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T73" s="76"/>
       <c r="U73" s="94"/>
       <c r="V73" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W73" s="105"/>
-      <c r="X73" s="1"/>
-      <c r="Y73" s="1"/>
-      <c r="Z73" s="1"/>
+      <c r="X73" s="131"/>
+      <c r="Y73" s="132"/>
+      <c r="Z73" s="133"/>
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
@@ -5978,40 +6649,49 @@
       <c r="E74" s="67"/>
       <c r="F74" s="66"/>
       <c r="G74" s="74"/>
-      <c r="H74" s="73"/>
-      <c r="I74" s="73"/>
-      <c r="J74" s="73"/>
+      <c r="H74" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I74" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J74" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K74" s="68"/>
       <c r="L74" s="73"/>
       <c r="M74" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N74" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O74" s="90"/>
       <c r="P74" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q74" s="91"/>
       <c r="R74" s="96"/>
       <c r="S74" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T74" s="76"/>
       <c r="U74" s="94"/>
       <c r="V74" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W74" s="105"/>
-      <c r="X74" s="1"/>
-      <c r="Y74" s="1"/>
-      <c r="Z74" s="1"/>
+      <c r="X74" s="131"/>
+      <c r="Y74" s="132"/>
+      <c r="Z74" s="133"/>
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
@@ -6034,40 +6714,49 @@
       <c r="E75" s="67"/>
       <c r="F75" s="66"/>
       <c r="G75" s="74"/>
-      <c r="H75" s="73"/>
-      <c r="I75" s="73"/>
-      <c r="J75" s="73"/>
+      <c r="H75" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I75" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J75" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K75" s="68"/>
       <c r="L75" s="73"/>
       <c r="M75" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N75" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O75" s="90"/>
       <c r="P75" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q75" s="91"/>
       <c r="R75" s="96"/>
       <c r="S75" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T75" s="76"/>
       <c r="U75" s="94"/>
       <c r="V75" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W75" s="105"/>
-      <c r="X75" s="1"/>
-      <c r="Y75" s="1"/>
-      <c r="Z75" s="1"/>
+      <c r="X75" s="131"/>
+      <c r="Y75" s="132"/>
+      <c r="Z75" s="133"/>
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
@@ -6090,40 +6779,49 @@
       <c r="E76" s="67"/>
       <c r="F76" s="66"/>
       <c r="G76" s="74"/>
-      <c r="H76" s="73"/>
-      <c r="I76" s="73"/>
-      <c r="J76" s="73"/>
+      <c r="H76" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I76" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J76" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K76" s="68"/>
       <c r="L76" s="73"/>
       <c r="M76" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N76" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O76" s="90"/>
       <c r="P76" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q76" s="91"/>
       <c r="R76" s="96"/>
       <c r="S76" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T76" s="76"/>
       <c r="U76" s="94"/>
       <c r="V76" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W76" s="105"/>
-      <c r="X76" s="1"/>
-      <c r="Y76" s="1"/>
-      <c r="Z76" s="1"/>
+      <c r="X76" s="131"/>
+      <c r="Y76" s="132"/>
+      <c r="Z76" s="133"/>
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
@@ -6146,40 +6844,49 @@
       <c r="E77" s="67"/>
       <c r="F77" s="66"/>
       <c r="G77" s="74"/>
-      <c r="H77" s="73"/>
-      <c r="I77" s="73"/>
-      <c r="J77" s="73"/>
+      <c r="H77" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I77" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J77" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K77" s="68"/>
       <c r="L77" s="73"/>
       <c r="M77" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N77" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O77" s="90"/>
       <c r="P77" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q77" s="91"/>
       <c r="R77" s="96"/>
       <c r="S77" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T77" s="76"/>
       <c r="U77" s="94"/>
       <c r="V77" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W77" s="105"/>
-      <c r="X77" s="1"/>
-      <c r="Y77" s="1"/>
-      <c r="Z77" s="1"/>
+      <c r="X77" s="131"/>
+      <c r="Y77" s="132"/>
+      <c r="Z77" s="133"/>
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
@@ -6202,40 +6909,49 @@
       <c r="E78" s="67"/>
       <c r="F78" s="66"/>
       <c r="G78" s="74"/>
-      <c r="H78" s="73"/>
-      <c r="I78" s="73"/>
-      <c r="J78" s="73"/>
+      <c r="H78" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I78" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J78" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K78" s="68"/>
       <c r="L78" s="73"/>
       <c r="M78" s="73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N78" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O78" s="90"/>
       <c r="P78" s="73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q78" s="91"/>
       <c r="R78" s="96"/>
       <c r="S78" s="65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T78" s="76"/>
       <c r="U78" s="94"/>
       <c r="V78" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W78" s="105"/>
-      <c r="X78" s="1"/>
-      <c r="Y78" s="1"/>
-      <c r="Z78" s="1"/>
+      <c r="X78" s="131"/>
+      <c r="Y78" s="132"/>
+      <c r="Z78" s="133"/>
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
@@ -6258,9 +6974,18 @@
       <c r="E79" s="62"/>
       <c r="F79" s="63"/>
       <c r="G79" s="63"/>
-      <c r="H79" s="63"/>
-      <c r="I79" s="63"/>
-      <c r="J79" s="63"/>
+      <c r="H79" s="162">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="I79" s="73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J79" s="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K79" s="64"/>
       <c r="L79" s="73"/>
       <c r="M79" s="73"/>
@@ -6274,9 +6999,9 @@
       <c r="U79" s="95"/>
       <c r="V79" s="63"/>
       <c r="W79" s="107"/>
-      <c r="X79" s="1"/>
-      <c r="Y79" s="1"/>
-      <c r="Z79" s="1"/>
+      <c r="X79" s="131"/>
+      <c r="Y79" s="132"/>
+      <c r="Z79" s="133"/>
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
@@ -6299,9 +7024,18 @@
       <c r="E80" s="110"/>
       <c r="F80" s="111"/>
       <c r="G80" s="111"/>
-      <c r="H80" s="111"/>
-      <c r="I80" s="111"/>
-      <c r="J80" s="111"/>
+      <c r="H80" s="163">
+        <f>$H$12</f>
+        <v>0.05</v>
+      </c>
+      <c r="I80" s="73">
+        <f t="shared" ref="I80" si="8">F80*H80</f>
+        <v>0</v>
+      </c>
+      <c r="J80" s="73">
+        <f t="shared" ref="J80" si="9">I80*E80</f>
+        <v>0</v>
+      </c>
       <c r="K80" s="112"/>
       <c r="L80" s="113"/>
       <c r="M80" s="113"/>
@@ -6315,9 +7049,9 @@
       <c r="U80" s="117"/>
       <c r="V80" s="111"/>
       <c r="W80" s="118"/>
-      <c r="X80" s="1"/>
-      <c r="Y80" s="1"/>
-      <c r="Z80" s="1"/>
+      <c r="X80" s="134"/>
+      <c r="Y80" s="135"/>
+      <c r="Z80" s="136"/>
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
@@ -6495,7 +7229,7 @@
         <v>29</v>
       </c>
       <c r="P84" s="56">
-        <f>P38+P39+P40+P41+P42+P44+P45+P48+P49+P51+P52+P53+P54+P55+P56+P57+P58+P65+P66+P71+P72+P73+P77+P78</f>
+        <f>SUMIF($X$15:$X$80,1,$P$15:$P$80)</f>
         <v>0</v>
       </c>
       <c r="Q84" s="15"/>
@@ -6503,7 +7237,7 @@
         <v>29</v>
       </c>
       <c r="S84" s="56">
-        <f>S15+S16+S17+S18+S19+S20+S21+S22+S31+S32+S33+S34+S35+S36+S37+S43+S46+S47+S50+S67+S68+S69+S70+S74+S75+S76</f>
+        <f>SUMIF($Y$15:$Y$80,1,$S$15:$S$80)</f>
         <v>0</v>
       </c>
       <c r="T84" s="15"/>
@@ -6511,7 +7245,7 @@
         <v>29</v>
       </c>
       <c r="V84" s="56">
-        <f>V23+V24+V25+V26+V27+V28+V29+V30+V59+V60+V61+V62+V63+V64</f>
+        <f>SUMIF($Z$15:$Z$80,1,$V$15:$V$80)</f>
         <v>0</v>
       </c>
       <c r="W84" s="15"/>
@@ -44325,8 +45059,12 @@
       <c r="AM1006" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B3:W3"/>
+  <mergeCells count="18">
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="R12:T12"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="X12:Z12"/>
+    <mergeCell ref="B3:Z3"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D13"/>
@@ -44340,19 +45078,21 @@
     <mergeCell ref="L12:L13"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="I12:I13"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="R12:T12"/>
-    <mergeCell ref="U12:W12"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="N14:N15 N79:N80">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16:N78">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X15:Z80">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
